--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-29 15:35 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-29 18:48 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-29 18:48 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-29 21:40 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-29 21:40 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-30 00:52 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-30 00:52 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-30 03:46 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-30 03:46 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-30 06:53 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-30 06:53 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-30 09:50 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-30 09:50 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-30 12:51 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-30 12:51 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-30 15:50 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-30 15:50 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-30 18:45 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-30 18:45 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-30 21:37 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-30 21:37 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-31 00:55 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-31 00:55 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-31 03:42 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-31 03:42 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-31 06:48 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-31 06:48 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-31 09:38 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-31 09:38 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-31 12:45 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-31 12:45 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-31 15:36 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-31 15:36 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-31 18:40 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>

--- a/copy_tracker.xlsx
+++ b/copy_tracker.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Copy-Trade Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed 2026-10-31 18:40 UTC</t>
+    <t xml:space="preserve">Refreshed 2026-10-31 21:35 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Your unit</t>
